--- a/test-data/Templates/SHS/M6 - Create Material type SEMI-FINISHED (DRIN.xlsx
+++ b/test-data/Templates/SHS/M6 - Create Material type SEMI-FINISHED (DRIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/SHS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF6557F-1732-2B4D-AAB3-4E29C3CFE8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A51116-2F3E-7246-8775-87C1DD7C7D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Step 170" sheetId="12" r:id="rId4"/>
     <sheet name="Step 400" sheetId="6" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="148">
   <si>
     <t>Object</t>
   </si>
@@ -351,9 +351,6 @@
     <t>Profit Center</t>
   </si>
   <si>
-    <t>Warehouse Number</t>
-  </si>
-  <si>
     <t>Prod. stor. Location</t>
   </si>
   <si>
@@ -417,14 +414,83 @@
     <t>01012100</t>
   </si>
   <si>
-    <t>TD61</t>
+    <t>TD71</t>
+  </si>
+  <si>
+    <t>^HALB</t>
+  </si>
+  <si>
+    <t>^L</t>
+  </si>
+  <si>
+    <t>^Z1</t>
+  </si>
+  <si>
+    <t>^NORM</t>
+  </si>
+  <si>
+    <t>^TD71</t>
+  </si>
+  <si>
+    <t>^Test Desc</t>
+  </si>
+  <si>
+    <t>^BG01</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>^BGN1</t>
+  </si>
+  <si>
+    <t>^1</t>
+  </si>
+  <si>
+    <t>^MM</t>
+  </si>
+  <si>
+    <t>^KG</t>
+  </si>
+  <si>
+    <t>^TD41</t>
+  </si>
+  <si>
+    <t>BG01</t>
+  </si>
+  <si>
+    <t>^030</t>
+  </si>
+  <si>
+    <t>^MWST</t>
+  </si>
+  <si>
+    <t>^GB</t>
+  </si>
+  <si>
+    <t>^United Kingdom</t>
+  </si>
+  <si>
+    <t>^Input tax</t>
+  </si>
+  <si>
+    <t>^ZR</t>
+  </si>
+  <si>
+    <t>^0001</t>
+  </si>
+  <si>
+    <t>S009</t>
+  </si>
+  <si>
+    <t>PC_BGN008</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -454,13 +520,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFEA0203"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFEA0203"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -475,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -490,12 +592,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFEA0203"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -868,7 +981,7 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
@@ -877,7 +990,7 @@
         <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -913,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -927,7 +1040,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
@@ -941,7 +1054,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -955,7 +1068,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
@@ -1048,22 +1161,22 @@
       <c r="B2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="11" t="s">
         <v>68</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1082,14 +1195,26 @@
       <c r="A3">
         <v>1</v>
       </c>
+      <c r="B3" s="12" t="s">
+        <v>125</v>
+      </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
         <v>81</v>
       </c>
+      <c r="E3" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>127</v>
+      </c>
       <c r="H3" s="4" t="s">
         <v>99</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="4"/>
@@ -1123,7 +1248,7 @@
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E6" s="1"/>
@@ -1131,6 +1256,15 @@
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -1168,6 +1302,18 @@
       <c r="A11">
         <v>1</v>
       </c>
+      <c r="B11" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
@@ -1199,14 +1345,24 @@
       <c r="E14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -1279,12 +1435,42 @@
       <c r="A19">
         <v>1</v>
       </c>
+      <c r="B19" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" t="s">
+        <v>126</v>
+      </c>
       <c r="G19" s="4"/>
+      <c r="I19" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" t="s">
+        <v>135</v>
+      </c>
+      <c r="P19" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
+      <c r="B20" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>130</v>
+      </c>
       <c r="D20">
         <v>11</v>
       </c>
@@ -1292,11 +1478,20 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G20" s="4"/>
+      <c r="I20" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="M20" t="s">
+        <v>135</v>
+      </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
+      <c r="P20" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
@@ -1334,7 +1529,7 @@
       <c r="F23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="9" t="s">
         <v>71</v>
       </c>
       <c r="H23" s="1" t="s">
@@ -1345,7 +1540,19 @@
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="G24" s="4"/>
+      <c r="B24" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="13">
+        <v>30</v>
+      </c>
+      <c r="E24" s="13"/>
+      <c r="G24" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -1380,7 +1587,7 @@
       <c r="F27" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -1396,7 +1603,25 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="G28" s="4"/>
+      <c r="B28" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H28" s="13"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -1444,6 +1669,30 @@
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H32" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
@@ -1482,6 +1731,15 @@
       <c r="A36">
         <v>1</v>
       </c>
+      <c r="B36" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -1513,10 +1771,10 @@
       <c r="E39" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="8" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1524,11 +1782,23 @@
       <c r="A40">
         <v>1</v>
       </c>
+      <c r="B40" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>145</v>
+      </c>
       <c r="F40" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -1562,7 +1832,7 @@
         <v>40</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>55</v>
@@ -1577,13 +1847,13 @@
         <v>50</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>56</v>
@@ -1655,7 +1925,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>83</v>
@@ -1684,19 +1954,19 @@
         <v>40</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="I51" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -1706,7 +1976,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>83</v>
@@ -1735,7 +2005,7 @@
         <v>40</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -2214,7 +2484,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>61</v>
@@ -2586,7 +2856,7 @@
         <v>40</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>55</v>
@@ -2601,13 +2871,13 @@
         <v>50</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>84</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>56</v>
@@ -2675,7 +2945,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>83</v>
@@ -2704,7 +2974,7 @@
         <v>40</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
@@ -2754,7 +3024,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>83</v>
@@ -2783,19 +3053,19 @@
         <v>40</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="I39" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -2880,7 +3150,7 @@
         <v>40</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>61</v>

--- a/test-data/Templates/SHS/M6 - Create Material type SEMI-FINISHED (DRIN.xlsx
+++ b/test-data/Templates/SHS/M6 - Create Material type SEMI-FINISHED (DRIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/SHS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A51116-2F3E-7246-8775-87C1DD7C7D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8512421-AFBD-2A4A-A4B1-C56D696E9865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -577,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -596,7 +596,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1088,8 +1087,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{867B6D3F-F6EA-6D45-89A3-70B9CE3A4229}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D9" xr:uid="{58227CB0-C6D9-A247-A15C-D0FCE8718EAF}">
-      <formula1>"Save,Skip,Approve,Reject -&gt; Approve"</formula1>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D9" xr:uid="{E765882D-FF84-CF42-9B87-DFBF6F71A80F}">
+      <formula1>"Save,Skip,Approve,Skip -&gt; Save,Skip -&gt; Approve,Reject -&gt; Approve"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1260,7 +1259,7 @@
       <c r="B7" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>130</v>
       </c>
       <c r="D7" t="s">
@@ -1305,7 +1304,7 @@
       <c r="B11" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>130</v>
       </c>
       <c r="D11" t="s">
@@ -1355,7 +1354,7 @@
       <c r="B15" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>130</v>
       </c>
       <c r="D15" t="s">
@@ -1438,7 +1437,7 @@
       <c r="B19" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>130</v>
       </c>
       <c r="D19" t="s">
@@ -1451,7 +1450,7 @@
         <v>126</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="12" t="s">
         <v>126</v>
       </c>
       <c r="M19" t="s">
@@ -1468,7 +1467,7 @@
       <c r="B20" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>130</v>
       </c>
       <c r="D20">
@@ -1481,7 +1480,7 @@
         <v>113</v>
       </c>
       <c r="G20" s="4"/>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="12" t="s">
         <v>126</v>
       </c>
       <c r="M20" t="s">
@@ -1540,16 +1539,16 @@
       <c r="A24">
         <v>1</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <v>30</v>
       </c>
-      <c r="E24" s="13"/>
+      <c r="E24" s="12"/>
       <c r="G24" s="4" t="s">
         <v>139</v>
       </c>
@@ -1603,25 +1602,25 @@
       <c r="A28">
         <v>1</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="12" t="s">
         <v>143</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="H28" s="13"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -1670,22 +1669,22 @@
       <c r="A32">
         <v>1</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="12" t="s">
         <v>145</v>
       </c>
       <c r="H32" t="s">
@@ -1731,13 +1730,13 @@
       <c r="A36">
         <v>1</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1782,16 +1781,16 @@
       <c r="A40">
         <v>1</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="12" t="s">
         <v>145</v>
       </c>
       <c r="F40" s="4" t="s">
